--- a/amazon_product.xlsx
+++ b/amazon_product.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,25 +439,40 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>availability</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>current_price</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>list_price</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Room Type</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Shape</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Product Dimensions</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Frame Material</t>
         </is>
@@ -471,12 +486,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41WWWUsearL._AC_SL1500_.jpg, https://m.media-amazon.com/images/I/41f6GMLi9fL._AC_SL1500_.jpg, https://m.media-amazon.com/images/I/410LQS1YdML._AC_SL1500_.jpg, https://m.media-amazon.com/images/I/41kkWRemjdL._AC_SL1500_.jpg, https://m.media-amazon.com/images/I/51hO0Z8pGhL._AC_SL1500_.jpg, https://m.media-amazon.com/images/I/41disSIFKPL._AC_SL1500_.jpg, https://m.media-amazon.com/images/I/41LnNUlwVGL._AC_SL1500_.jpg</t>
+          <t>['https://m.media-amazon.com/images/I/41WWWUsearL._AC_SL1500_.jpg', 'https://m.media-amazon.com/images/I/41kkWRemjdL._AC_SL1500_.jpg', 'https://m.media-amazon.com/images/I/41f6GMLi9fL._AC_SL1500_.jpg', 'https://m.media-amazon.com/images/I/410LQS1YdML._AC_SL1500_.jpg', 'https://m.media-amazon.com/images/I/51hO0Z8pGhL._AC_SL1500_.jpg', 'https://m.media-amazon.com/images/I/41disSIFKPL._AC_SL1500_.jpg', 'https://m.media-amazon.com/images/I/41LnNUlwVGL._AC_SL1500_.jpg']</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>46.6"L x 13.6"W, 47"L x 14"W, 55.3"L x 20.4"W, 55.5"L x 14.6"W, 56"L x 15"W, 56"L x 21"W, 57.3"L x 18.4"W, 58"L x 19"W, 59"L x 16"W, 59.1"L x 15.8"W, 63.6"L x 20.6"W, 64"L x 21"W, 64.4"L x 23.4"W, 65"L x 24"W, 66.9"L x 25.4"W, 68"L x 26"W, 70.4"L x 25.6"W, 71"L x 26"W</t>
+          <t>['47"L x 14"W', '55.3"L x 20.4"W', '55.5"L x 14.6"W', '56"L x 15"W', '56"L x 21"W', '57.3"L x 18.4"W', '58"L x 19"W', '59"L x 16"W', '59.1"L x 15.8"W', '63.6"L x 20.6"W', '64"L x 21"W', '64.4"L x 23.4"W', '65"L x 24"W', '66.9"L x 25.4"W', '68"L x 26"W', '70.4"L x 25.6"W', '71"L x 26"W']</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -486,25 +501,40 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>$32.99</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>$49.99</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>DUMOS</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Bedroom, Dressing Room, Living Room</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Arched-top</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>55.51"L x 14.57"W</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Aluminum</t>
         </is>
